--- a/data/dividends_info_20260513.xlsx
+++ b/data/dividends_info_20260513.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.2599983215332</v>
+        <v>52.34000015258789</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1790688480016139</v>
+        <v>0.1719526169996582</v>
       </c>
       <c r="J2" t="n">
         <v>306</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57.09999847412109</v>
+        <v>57.54999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.225919472339837</v>
+        <v>1.216333639061493</v>
       </c>
       <c r="J3" t="n">
         <v>285</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.560000419616699</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6276150352136245</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J4" t="n">
         <v>215</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>50.2599983215332</v>
+        <v>52.34000015258789</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1790688480016139</v>
+        <v>0.1719526169996582</v>
       </c>
       <c r="J6" t="n">
         <v>215</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.059999942779541</v>
+        <v>2.035000085830688</v>
       </c>
       <c r="I7" t="n">
-        <v>3.737864181496264</v>
+        <v>3.783783624194224</v>
       </c>
       <c r="J7" t="n">
         <v>194</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.82999992370605</v>
+        <v>23.56999969482422</v>
       </c>
       <c r="I8" t="n">
-        <v>1.133025601613219</v>
+        <v>1.145523985981594</v>
       </c>
       <c r="J8" t="n">
         <v>194</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.789999961853027</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I9" t="n">
-        <v>3.454231456263985</v>
+        <v>3.442340825640675</v>
       </c>
       <c r="J9" t="n">
         <v>187</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.5</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.923076923076923</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J10" t="n">
         <v>159</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.199999809265137</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9615384968074835</v>
+        <v>0.9689922767163736</v>
       </c>
       <c r="J12" t="n">
         <v>145</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.76</v>
       </c>
       <c r="J13" t="n">
         <v>138</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.82500076293945</v>
+        <v>23.56999969482422</v>
       </c>
       <c r="I14" t="n">
-        <v>1.133263342513691</v>
+        <v>1.145523985981594</v>
       </c>
       <c r="J14" t="n">
         <v>131</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50.2599983215332</v>
+        <v>52.34000015258789</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1790688480016139</v>
+        <v>0.1719526169996582</v>
       </c>
       <c r="J15" t="n">
         <v>131</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4.980000019073486</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.76</v>
       </c>
       <c r="J17" t="n">
         <v>82</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.940000057220459</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I18" t="n">
-        <v>4.208754168210969</v>
+        <v>4.230118552532127</v>
       </c>
       <c r="J18" t="n">
         <v>75</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.803000450134277</v>
+        <v>9.737000465393066</v>
       </c>
       <c r="I19" t="n">
-        <v>2.652249189649263</v>
+        <v>2.670226841665292</v>
       </c>
       <c r="J19" t="n">
         <v>68</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15.22000026702881</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="I20" t="n">
-        <v>3.942181271177663</v>
+        <v>3.963011799168287</v>
       </c>
       <c r="J20" t="n">
         <v>68</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3.598000049591064</v>
+        <v>3.618000030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>6.114507975757377</v>
+        <v>6.080707521954542</v>
       </c>
       <c r="J21" t="n">
         <v>68</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.099999904632568</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I23" t="n">
-        <v>3.934426291019038</v>
+        <v>3.92156870078234</v>
       </c>
       <c r="J23" t="n">
         <v>68</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>18.5</v>
+        <v>18.25</v>
       </c>
       <c r="I24" t="n">
-        <v>2.032432432432433</v>
+        <v>2.06027397260274</v>
       </c>
       <c r="J24" t="n">
         <v>68</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5.349999904632568</v>
+        <v>5.289999961853027</v>
       </c>
       <c r="I25" t="n">
-        <v>2.24299069418846</v>
+        <v>2.26843101824835</v>
       </c>
       <c r="J25" t="n">
         <v>61</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.180000066757202</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I27" t="n">
-        <v>3.899082449407415</v>
+        <v>3.828828779484834</v>
       </c>
       <c r="J27" t="n">
         <v>54</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.389999866485596</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="I28" t="n">
-        <v>1.594533078107776</v>
+        <v>1.601830705564068</v>
       </c>
       <c r="J28" t="n">
         <v>54</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>34.34999847412109</v>
+        <v>33.75</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4366812421054642</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J29" t="n">
         <v>54</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>23.73999977111816</v>
+        <v>23.55999946594238</v>
       </c>
       <c r="I31" t="n">
-        <v>4.001684958547304</v>
+        <v>4.032258155919278</v>
       </c>
       <c r="J31" t="n">
         <v>40</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>26.85000038146973</v>
+        <v>27.14999961853027</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7262569729219721</v>
+        <v>0.7182320542903788</v>
       </c>
       <c r="J32" t="n">
         <v>40</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.840000033378601</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="I33" t="n">
-        <v>1.793478228334894</v>
+        <v>1.823204477527402</v>
       </c>
       <c r="J33" t="n">
         <v>40</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4.849999904632568</v>
+        <v>4.828000068664551</v>
       </c>
       <c r="I34" t="n">
-        <v>5.979381560873867</v>
+        <v>6.006627917886824</v>
       </c>
       <c r="J34" t="n">
         <v>40</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.895999908447266</v>
+        <v>3.855999946594238</v>
       </c>
       <c r="I35" t="n">
-        <v>4.106776277203952</v>
+        <v>4.149377650830051</v>
       </c>
       <c r="J35" t="n">
         <v>40</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.782000064849854</v>
+        <v>2.730000019073486</v>
       </c>
       <c r="I36" t="n">
-        <v>4.982027202342295</v>
+        <v>5.076923041452519</v>
       </c>
       <c r="J36" t="n">
         <v>40</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>49.61999893188477</v>
+        <v>49.84000015258789</v>
       </c>
       <c r="I37" t="n">
-        <v>1.269649362275934</v>
+        <v>1.264044939950282</v>
       </c>
       <c r="J37" t="n">
         <v>40</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.195000171661377</v>
+        <v>5.230000019073486</v>
       </c>
       <c r="I38" t="n">
-        <v>2.694898852240607</v>
+        <v>2.676864234979516</v>
       </c>
       <c r="J38" t="n">
         <v>40</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>18.89999961853027</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="I39" t="n">
-        <v>4.126984210281457</v>
+        <v>4.08376955194584</v>
       </c>
       <c r="J39" t="n">
         <v>40</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>23.84000015258789</v>
+        <v>24.01000022888184</v>
       </c>
       <c r="I40" t="n">
-        <v>3.565436218790168</v>
+        <v>3.540191553090981</v>
       </c>
       <c r="J40" t="n">
         <v>40</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>50.2599983215332</v>
+        <v>52.34000015258789</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1790688480016139</v>
+        <v>0.1719526169996582</v>
       </c>
       <c r="J41" t="n">
         <v>40</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.455999851226807</v>
+        <v>6.401999950408936</v>
       </c>
       <c r="I43" t="n">
-        <v>2.808240461243944</v>
+        <v>2.831927544585802</v>
       </c>
       <c r="J43" t="n">
         <v>40</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8.489999771118164</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="I44" t="n">
-        <v>3.062426466541083</v>
+        <v>3.044496500718773</v>
       </c>
       <c r="J44" t="n">
         <v>40</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>9.904000282287598</v>
+        <v>9.918000221252441</v>
       </c>
       <c r="I45" t="n">
-        <v>2.796849677956788</v>
+        <v>2.792901732412147</v>
       </c>
       <c r="J45" t="n">
         <v>40</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.184999942779541</v>
+        <v>1.195000052452087</v>
       </c>
       <c r="I46" t="n">
-        <v>1.139240561339973</v>
+        <v>1.129707063384524</v>
       </c>
       <c r="J46" t="n">
         <v>33</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3.757999897003174</v>
+        <v>3.727999925613403</v>
       </c>
       <c r="I47" t="n">
-        <v>2.927088957286022</v>
+        <v>2.950643835699665</v>
       </c>
       <c r="J47" t="n">
         <v>33</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.160000085830688</v>
+        <v>3.105000019073486</v>
       </c>
       <c r="I49" t="n">
-        <v>5.063291001713369</v>
+        <v>5.152979034368672</v>
       </c>
       <c r="J49" t="n">
         <v>26</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>27.20000076293945</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I51" t="n">
-        <v>4.080882238475512</v>
+        <v>4.051094946911317</v>
       </c>
       <c r="J51" t="n">
         <v>22</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="I52" t="n">
-        <v>3.333333421636513</v>
+        <v>3.296703201692877</v>
       </c>
       <c r="J52" t="n">
         <v>19</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.5109999775886536</v>
+        <v>0.503000020980835</v>
       </c>
       <c r="I53" t="n">
-        <v>4.500978670984329</v>
+        <v>4.572564421597973</v>
       </c>
       <c r="J53" t="n">
         <v>19</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>20.5</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="I54" t="n">
-        <v>2.926829268292683</v>
+        <v>2.970296917516995</v>
       </c>
       <c r="J54" t="n">
         <v>19</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>9</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I55" t="n">
-        <v>2.222222222222222</v>
+        <v>2.272727223467237</v>
       </c>
       <c r="J55" t="n">
         <v>19</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.494999885559082</v>
+        <v>2.505000114440918</v>
       </c>
       <c r="I56" t="n">
-        <v>7.214429188627615</v>
+        <v>7.185628414239556</v>
       </c>
       <c r="J56" t="n">
         <v>12</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8.149999618530273</v>
+        <v>8.25</v>
       </c>
       <c r="I57" t="n">
-        <v>3.68098176738443</v>
+        <v>3.636363636363636</v>
       </c>
       <c r="J57" t="n">
         <v>12</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>13.84000015258789</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="I58" t="n">
-        <v>1.806358361587542</v>
+        <v>1.788269014206337</v>
       </c>
       <c r="J58" t="n">
         <v>12</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.470000028610229</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8645533069927757</v>
+        <v>0.8670520135620203</v>
       </c>
       <c r="J59" t="n">
         <v>12</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3.829999923706055</v>
+        <v>3.819999933242798</v>
       </c>
       <c r="I60" t="n">
-        <v>3.9164491641779</v>
+        <v>3.926701639302517</v>
       </c>
       <c r="J60" t="n">
         <v>12</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14</v>
+        <v>13.85000038146973</v>
       </c>
       <c r="I61" t="n">
-        <v>4.142857142857142</v>
+        <v>4.187725516426678</v>
       </c>
       <c r="J61" t="n">
         <v>12</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2.341000080108643</v>
+        <v>2.313999891281128</v>
       </c>
       <c r="I62" t="n">
-        <v>4.442545768523575</v>
+        <v>4.494382233631879</v>
       </c>
       <c r="J62" t="n">
         <v>5</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>10.64999961853027</v>
+        <v>10.67500019073486</v>
       </c>
       <c r="I63" t="n">
-        <v>2.723004792370318</v>
+        <v>2.716627586121256</v>
       </c>
       <c r="J63" t="n">
         <v>5</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.059999942779541</v>
+        <v>2.035000085830688</v>
       </c>
       <c r="I64" t="n">
-        <v>3.737864181496264</v>
+        <v>3.783783624194224</v>
       </c>
       <c r="J64" t="n">
         <v>5</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>38.84000015258789</v>
+        <v>38.88000106811523</v>
       </c>
       <c r="I65" t="n">
-        <v>4.222451064770985</v>
+        <v>4.21810688000452</v>
       </c>
       <c r="J65" t="n">
         <v>5</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>35.63999938964844</v>
+        <v>35.84999847412109</v>
       </c>
       <c r="I66" t="n">
-        <v>5.611672374441442</v>
+        <v>5.578800795329832</v>
       </c>
       <c r="J66" t="n">
         <v>5</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3.759999990463257</v>
+        <v>3.716000080108643</v>
       </c>
       <c r="I67" t="n">
-        <v>2.659574474830765</v>
+        <v>2.691065603988802</v>
       </c>
       <c r="J67" t="n">
         <v>5</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>30.80999946594238</v>
+        <v>29.61000061035156</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4818565484368439</v>
+        <v>0.5013846570070616</v>
       </c>
       <c r="J68" t="n">
         <v>5</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>20.45999908447266</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="I69" t="n">
-        <v>4.496578891336311</v>
+        <v>4.466019334774215</v>
       </c>
       <c r="J69" t="n">
         <v>5</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>10.69999980926514</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="I70" t="n">
-        <v>2.803738367735575</v>
+        <v>2.69541776204258</v>
       </c>
       <c r="J70" t="n">
         <v>5</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>80.86000061035156</v>
+        <v>83.04000091552734</v>
       </c>
       <c r="I71" t="n">
-        <v>1.286173623732153</v>
+        <v>1.252408464034029</v>
       </c>
       <c r="J71" t="n">
         <v>5</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>46.65000152587891</v>
+        <v>46.81999969482422</v>
       </c>
       <c r="I72" t="n">
-        <v>1.500535856599442</v>
+        <v>1.495087579159857</v>
       </c>
       <c r="J72" t="n">
         <v>5</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>57.04999923706055</v>
+        <v>57.54999923706055</v>
       </c>
       <c r="I73" t="n">
-        <v>3.856266484524065</v>
+        <v>3.822762865621836</v>
       </c>
       <c r="J73" t="n">
         <v>5</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>9.517000198364258</v>
+        <v>9.487000465393066</v>
       </c>
       <c r="I74" t="n">
-        <v>9.036460881316501</v>
+        <v>9.065035920859611</v>
       </c>
       <c r="J74" t="n">
         <v>5</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>12.36999988555908</v>
+        <v>12.48600006103516</v>
       </c>
       <c r="I75" t="n">
-        <v>4.527081691033419</v>
+        <v>4.485023204089053</v>
       </c>
       <c r="J75" t="n">
         <v>5</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.240000009536743</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I78" t="n">
-        <v>4.821428550901461</v>
+        <v>4.843049285931015</v>
       </c>
       <c r="J78" t="n">
         <v>5</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>85.30000305175781</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="I79" t="n">
-        <v>2.415005775263626</v>
+        <v>2.370540809929135</v>
       </c>
       <c r="J79" t="n">
         <v>5</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>15.56999969482422</v>
+        <v>15.5600004196167</v>
       </c>
       <c r="I80" t="n">
-        <v>4.81695577842121</v>
+        <v>4.820051283896272</v>
       </c>
       <c r="J80" t="n">
         <v>5</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>14.78999996185303</v>
+        <v>14.71000003814697</v>
       </c>
       <c r="I81" t="n">
-        <v>2.028397571154647</v>
+        <v>2.039428954602444</v>
       </c>
       <c r="J81" t="n">
         <v>5</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>52.40000152587891</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I82" t="n">
-        <v>1.622137357343794</v>
+        <v>1.579925672962595</v>
       </c>
       <c r="J82" t="n">
         <v>5</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>36.15999984741211</v>
+        <v>36.84000015258789</v>
       </c>
       <c r="I83" t="n">
-        <v>2.350663726733485</v>
+        <v>2.30727469185499</v>
       </c>
       <c r="J83" t="n">
         <v>5</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>70.04000091552734</v>
+        <v>70.54000091552734</v>
       </c>
       <c r="I84" t="n">
-        <v>1.856082214458966</v>
+        <v>1.842925975513905</v>
       </c>
       <c r="J84" t="n">
         <v>5</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>7.940000057220459</v>
+        <v>7.800000190734863</v>
       </c>
       <c r="I85" t="n">
-        <v>7.556675008514306</v>
+        <v>7.692307504206254</v>
       </c>
       <c r="J85" t="n">
         <v>5</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.789999961853027</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I87" t="n">
-        <v>3.454231456263985</v>
+        <v>3.442340825640675</v>
       </c>
       <c r="J87" t="n">
         <v>5</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>23.1200008392334</v>
+        <v>22.8799991607666</v>
       </c>
       <c r="I88" t="n">
-        <v>4.325259358568248</v>
+        <v>4.370629530943106</v>
       </c>
       <c r="J88" t="n">
         <v>5</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>4.820000171661377</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="I89" t="n">
-        <v>4.460580754002192</v>
+        <v>4.535865197927669</v>
       </c>
       <c r="J89" t="n">
         <v>5</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.82500076293945</v>
+        <v>23.56999969482422</v>
       </c>
       <c r="I90" t="n">
-        <v>1.133263342513691</v>
+        <v>1.145523985981594</v>
       </c>
       <c r="J90" t="n">
         <v>5</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>8.710000038146973</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="I92" t="n">
-        <v>2.755453489654167</v>
+        <v>2.752293493699352</v>
       </c>
       <c r="J92" t="n">
         <v>5</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>21.22999954223633</v>
+        <v>21.43000030517578</v>
       </c>
       <c r="I93" t="n">
-        <v>3.721149397240085</v>
+        <v>3.686420852776185</v>
       </c>
       <c r="J93" t="n">
         <v>5</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5.260000228881836</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I94" t="n">
-        <v>1.768060759567112</v>
+        <v>1.761363566373337</v>
       </c>
       <c r="J94" t="n">
         <v>5</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>6.5</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="I95" t="n">
-        <v>0.923076923076923</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J95" t="n">
         <v>5</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>35.34000015258789</v>
+        <v>35.81999969482422</v>
       </c>
       <c r="I96" t="n">
-        <v>0.990379169464633</v>
+        <v>0.9771077693520276</v>
       </c>
       <c r="J96" t="n">
         <v>5</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.099999904632568</v>
+        <v>7.105000019073486</v>
       </c>
       <c r="I97" t="n">
-        <v>7.807042358385575</v>
+        <v>7.801548184545712</v>
       </c>
       <c r="J97" t="n">
         <v>5</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2.269999980926514</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I98" t="n">
-        <v>2.643171828376432</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J98" t="n">
         <v>5</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>13</v>
+        <v>13.05000019073486</v>
       </c>
       <c r="I99" t="n">
-        <v>1.538461538461539</v>
+        <v>1.532567027408892</v>
       </c>
       <c r="J99" t="n">
         <v>5</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.965000152587891</v>
+        <v>7.014999866485596</v>
       </c>
       <c r="I100" t="n">
-        <v>1.478822652455071</v>
+        <v>1.468282280261844</v>
       </c>
       <c r="J100" t="n">
         <v>5</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5.757999897003174</v>
+        <v>5.714000225067139</v>
       </c>
       <c r="I101" t="n">
-        <v>3.299756919045587</v>
+        <v>3.325166127338883</v>
       </c>
       <c r="J101" t="n">
         <v>5</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>10.38000011444092</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I102" t="n">
-        <v>4.161849665097698</v>
+        <v>4.194174679614045</v>
       </c>
       <c r="J102" t="n">
         <v>5</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>26.10000038146973</v>
+        <v>26.11000061035156</v>
       </c>
       <c r="I103" t="n">
-        <v>1.685823730149781</v>
+        <v>1.685178053291801</v>
       </c>
       <c r="J103" t="n">
         <v>5</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>8.300000190734863</v>
+        <v>8.359999656677246</v>
       </c>
       <c r="I105" t="n">
-        <v>5.662650472281341</v>
+        <v>5.622009800258838</v>
       </c>
       <c r="J105" t="n">
         <v>5</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>49.45999908447266</v>
+        <v>50.79999923706055</v>
       </c>
       <c r="I106" t="n">
-        <v>2.830570210098351</v>
+        <v>2.755905553200572</v>
       </c>
       <c r="J106" t="n">
         <v>5</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>3.877000093460083</v>
+        <v>3.813999891281128</v>
       </c>
       <c r="I107" t="n">
-        <v>7.737941520972748</v>
+        <v>7.865757958876856</v>
       </c>
       <c r="J107" t="n">
         <v>5</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>13</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="I108" t="n">
-        <v>0.923076923076923</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J108" t="n">
         <v>5</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.470000028610229</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="I109" t="n">
-        <v>4.899135406292396</v>
+        <v>4.871060158609155</v>
       </c>
       <c r="J109" t="n">
         <v>5</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>22.25</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="I110" t="n">
-        <v>3.146067415730337</v>
+        <v>3.19634708763971</v>
       </c>
       <c r="J110" t="n">
         <v>5</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>2.380000114440918</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I111" t="n">
-        <v>1.47058816458174</v>
+        <v>1.495726550589419</v>
       </c>
       <c r="J111" t="n">
         <v>5</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>5.71999979019165</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="I112" t="n">
-        <v>5.769230980844901</v>
+        <v>5.799648447828024</v>
       </c>
       <c r="J112" t="n">
         <v>5</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.9779999852180481</v>
+        <v>0.9810000061988831</v>
       </c>
       <c r="I113" t="n">
-        <v>7.157464320860218</v>
+        <v>7.135575897826096</v>
       </c>
       <c r="J113" t="n">
         <v>5</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>50.5</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="I114" t="n">
-        <v>1.405940594059406</v>
+        <v>1.370656390844167</v>
       </c>
       <c r="J114" t="n">
         <v>5</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>92.44999694824219</v>
+        <v>91.44999694824219</v>
       </c>
       <c r="I115" t="n">
-        <v>1.460248831328564</v>
+        <v>1.476216561017555</v>
       </c>
       <c r="J115" t="n">
         <v>5</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>7.079999923706055</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I116" t="n">
-        <v>1.129943515001109</v>
+        <v>1.126760578514967</v>
       </c>
       <c r="J116" t="n">
         <v>5</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>4.578999996185303</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="I118" t="n">
-        <v>3.712601007679067</v>
+        <v>3.703703580579452</v>
       </c>
       <c r="J118" t="n">
         <v>5</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>58.70000076293945</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7666098707857425</v>
+        <v>0.7601351253389008</v>
       </c>
       <c r="J120" t="n">
         <v>5</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>5.179999828338623</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7722007977909368</v>
+        <v>0.7874015866287349</v>
       </c>
       <c r="J121" t="n">
         <v>5</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>37.70000076293945</v>
+        <v>38.91999816894531</v>
       </c>
       <c r="I122" t="n">
-        <v>2.785145832230832</v>
+        <v>2.697841853543062</v>
       </c>
       <c r="J122" t="n">
         <v>5</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1.549999952316284</v>
+        <v>1.5</v>
       </c>
       <c r="I123" t="n">
-        <v>3.225806550850609</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J123" t="n">
         <v>5</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>21.29999923706055</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="I124" t="n">
-        <v>1.78403762258745</v>
+        <v>1.792452765682409</v>
       </c>
       <c r="J124" t="n">
         <v>5</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>26.79999923706055</v>
+        <v>27.15999984741211</v>
       </c>
       <c r="I125" t="n">
-        <v>2.238806033883338</v>
+        <v>2.209131087521599</v>
       </c>
       <c r="J125" t="n">
         <v>5</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>32.25</v>
+        <v>31.79999923706055</v>
       </c>
       <c r="I126" t="n">
-        <v>1.085271317829457</v>
+        <v>1.100628957223687</v>
       </c>
       <c r="J126" t="n">
         <v>5</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.839999914169312</v>
+        <v>2.815000057220459</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3521126866979135</v>
+        <v>0.3552397796351747</v>
       </c>
       <c r="J128" t="n">
         <v>5</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>22.13999938964844</v>
+        <v>22.28000068664551</v>
       </c>
       <c r="I129" t="n">
-        <v>5.058717393297022</v>
+        <v>5.026929827122138</v>
       </c>
       <c r="J129" t="n">
         <v>5</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>8.899999618530273</v>
+        <v>8.779999732971191</v>
       </c>
       <c r="I131" t="n">
-        <v>2.921348439820898</v>
+        <v>2.961275716485869</v>
       </c>
       <c r="J131" t="n">
         <v>5</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2.075999975204468</v>
+        <v>2.108000040054321</v>
       </c>
       <c r="I132" t="n">
-        <v>4.446050149442283</v>
+        <v>4.378557791565388</v>
       </c>
       <c r="J132" t="n">
         <v>5</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>8.659999847412109</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="I133" t="n">
-        <v>4.041570510010938</v>
+        <v>4.032257922747988</v>
       </c>
       <c r="J133" t="n">
         <v>-2</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>5.050000190734863</v>
+        <v>5</v>
       </c>
       <c r="I134" t="n">
-        <v>1.900990027210877</v>
+        <v>1.92</v>
       </c>
       <c r="J134" t="n">
         <v>-2</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>6.099999904632568</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I135" t="n">
-        <v>4.918032863773797</v>
+        <v>4.958677529621045</v>
       </c>
       <c r="J135" t="n">
         <v>-2</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>12.10000038146973</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I136" t="n">
-        <v>1.652892509873682</v>
+        <v>1.70940173726859</v>
       </c>
       <c r="J136" t="n">
         <v>-2</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>9.560000419616699</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6276150352136245</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J137" t="n">
         <v>-2</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>19.65999984741211</v>
+        <v>19</v>
       </c>
       <c r="I138" t="n">
-        <v>2.543235014652435</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="J138" t="n">
         <v>-2</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>15.35999965667725</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="I140" t="n">
-        <v>3.255208406092911</v>
+        <v>3.306878331907552</v>
       </c>
       <c r="J140" t="n">
         <v>-2</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>4.119999885559082</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I141" t="n">
-        <v>2.427184533439133</v>
+        <v>2.512562802029314</v>
       </c>
       <c r="J141" t="n">
         <v>-2</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.650000095367432</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="I142" t="n">
-        <v>3.013698551394879</v>
+        <v>3.107344666253049</v>
       </c>
       <c r="J142" t="n">
         <v>-2</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>4.949999809265137</v>
+        <v>4.940000057220459</v>
       </c>
       <c r="I144" t="n">
-        <v>1.919191993142792</v>
+        <v>1.923076900801753</v>
       </c>
       <c r="J144" t="n">
         <v>-2</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>8.399999618530273</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I147" t="n">
-        <v>1.190476244539363</v>
+        <v>1.204819249421562</v>
       </c>
       <c r="J147" t="n">
         <v>-2</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>6.96999979019165</v>
+        <v>7.010000228881836</v>
       </c>
       <c r="I148" t="n">
-        <v>3.156384600033837</v>
+        <v>3.138373649312878</v>
       </c>
       <c r="J148" t="n">
         <v>-2</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>27.70000076293945</v>
+        <v>27.04999923706055</v>
       </c>
       <c r="I149" t="n">
-        <v>2.202166004327822</v>
+        <v>2.255083242901736</v>
       </c>
       <c r="J149" t="n">
         <v>-9</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>3</v>
+        <v>2.990000009536743</v>
       </c>
       <c r="I150" t="n">
-        <v>5</v>
+        <v>5.016722392025687</v>
       </c>
       <c r="J150" t="n">
         <v>-9</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>10.69999980926514</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="I151" t="n">
-        <v>6.542056191383009</v>
+        <v>6.603773347250979</v>
       </c>
       <c r="J151" t="n">
         <v>-9</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>8.560000419616699</v>
+        <v>8.510000228881836</v>
       </c>
       <c r="I152" t="n">
-        <v>5.963784754380411</v>
+        <v>5.998824750526201</v>
       </c>
       <c r="J152" t="n">
         <v>-9</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>8.539999961853027</v>
+        <v>8.255000114440918</v>
       </c>
       <c r="I153" t="n">
-        <v>3.161592519977188</v>
+        <v>3.270744957685396</v>
       </c>
       <c r="J153" t="n">
         <v>-9</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>6.364999771118164</v>
+        <v>6.295000076293945</v>
       </c>
       <c r="I154" t="n">
-        <v>5.498821878802898</v>
+        <v>5.559968161367449</v>
       </c>
       <c r="J154" t="n">
         <v>-9</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>40.79999923706055</v>
+        <v>42</v>
       </c>
       <c r="I155" t="n">
-        <v>2.696078481787859</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="J155" t="n">
         <v>-9</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>17.75</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="I156" t="n">
-        <v>4.225352112676056</v>
+        <v>4.237287952949482</v>
       </c>
       <c r="J156" t="n">
         <v>-9</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>10.80000019073486</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="I157" t="n">
-        <v>3.981481411165989</v>
+        <v>4.01869166042099</v>
       </c>
       <c r="J157" t="n">
         <v>-9</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>4.070000171661377</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="I158" t="n">
-        <v>3.68550353005931</v>
+        <v>3.676470656983444</v>
       </c>
       <c r="J158" t="n">
         <v>-9</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>12</v>
+        <v>11.76000022888184</v>
       </c>
       <c r="I159" t="n">
-        <v>1.643075</v>
+        <v>1.676607110225773</v>
       </c>
       <c r="J159" t="n">
         <v>-9</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>28.54999923706055</v>
+        <v>27.75</v>
       </c>
       <c r="I160" t="n">
-        <v>3.852889770210915</v>
+        <v>3.963963963963964</v>
       </c>
       <c r="J160" t="n">
         <v>-9</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>61.29999923706055</v>
+        <v>62.09999847412109</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7667210535882828</v>
+        <v>0.756843818918712</v>
       </c>
       <c r="J161" t="n">
         <v>-9</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>88.19999694824219</v>
+        <v>90</v>
       </c>
       <c r="I162" t="n">
-        <v>1.36054426476249</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="J162" t="n">
         <v>-9</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>24.70000076293945</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="I163" t="n">
-        <v>1.093117375142414</v>
+        <v>1.115702444164735</v>
       </c>
       <c r="J163" t="n">
         <v>-9</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>30.20000076293945</v>
+        <v>31.75</v>
       </c>
       <c r="I165" t="n">
-        <v>0.9933774583481174</v>
+        <v>0.9448818897637795</v>
       </c>
       <c r="J165" t="n">
         <v>-9</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>0.1736000031232834</v>
+        <v>0.1720000058412552</v>
       </c>
       <c r="I166" t="n">
-        <v>4.032257991970712</v>
+        <v>4.069767303647969</v>
       </c>
       <c r="J166" t="n">
         <v>-16</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>6.829999923706055</v>
+        <v>6.900000095367432</v>
       </c>
       <c r="I167" t="n">
-        <v>2.342606175509029</v>
+        <v>2.318840547660599</v>
       </c>
       <c r="J167" t="n">
         <v>-16</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>2.115000009536743</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I168" t="n">
-        <v>3.073286038151707</v>
+        <v>3.066037901358581</v>
       </c>
       <c r="J168" t="n">
         <v>-16</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>7.409999847412109</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I169" t="n">
-        <v>3.373819232767066</v>
+        <v>3.101736811223256</v>
       </c>
       <c r="J169" t="n">
         <v>-16</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>7.159999847412109</v>
+        <v>7.190000057220459</v>
       </c>
       <c r="I171" t="n">
-        <v>6.983240372284626</v>
+        <v>6.954102865380117</v>
       </c>
       <c r="J171" t="n">
         <v>-23</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>19.30999946594238</v>
+        <v>19.21500015258789</v>
       </c>
       <c r="I172" t="n">
-        <v>3.366131631160448</v>
+        <v>3.382773847714269</v>
       </c>
       <c r="J172" t="n">
         <v>-23</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>13.13500022888184</v>
+        <v>13.1899995803833</v>
       </c>
       <c r="I173" t="n">
-        <v>4.111153335289812</v>
+        <v>4.094010744345359</v>
       </c>
       <c r="J173" t="n">
         <v>-23</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>5.328000068664551</v>
+        <v>5.334000110626221</v>
       </c>
       <c r="I174" t="n">
-        <v>1.876876852688644</v>
+        <v>1.874765615410905</v>
       </c>
       <c r="J174" t="n">
         <v>-23</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>8.300000190734863</v>
+        <v>8.140000343322754</v>
       </c>
       <c r="I175" t="n">
-        <v>1.927710799074499</v>
+        <v>1.965601882698298</v>
       </c>
       <c r="J175" t="n">
         <v>-23</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>276.5</v>
+        <v>283.1499938964844</v>
       </c>
       <c r="I176" t="n">
-        <v>1.307414104882459</v>
+        <v>1.2767084859347</v>
       </c>
       <c r="J176" t="n">
         <v>-23</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>29.29999923706055</v>
+        <v>28.70000076293945</v>
       </c>
       <c r="I177" t="n">
-        <v>4.64163834611908</v>
+        <v>4.73867583221872</v>
       </c>
       <c r="J177" t="n">
         <v>-23</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>13.92500019073486</v>
+        <v>13.93000030517578</v>
       </c>
       <c r="I178" t="n">
-        <v>41.80682168947803</v>
+        <v>41.79181530840992</v>
       </c>
       <c r="J178" t="n">
         <v>-23</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>14.86999988555908</v>
+        <v>14.75</v>
       </c>
       <c r="I179" t="n">
-        <v>3.934095524560962</v>
+        <v>3.966101694915254</v>
       </c>
       <c r="J179" t="n">
         <v>-23</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>20.84000015258789</v>
+        <v>20.68000030517578</v>
       </c>
       <c r="I180" t="n">
-        <v>3.023032607424272</v>
+        <v>3.046421618486746</v>
       </c>
       <c r="J180" t="n">
         <v>-23</v>
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>152.1000061035156</v>
+        <v>154.6999969482422</v>
       </c>
       <c r="I181" t="n">
-        <v>0.5917159525868011</v>
+        <v>0.5817711814830301</v>
       </c>
       <c r="J181" t="n">
         <v>-23</v>
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>70.29000091552734</v>
+        <v>71.16000366210938</v>
       </c>
       <c r="I182" t="n">
-        <v>2.448143374002814</v>
+        <v>2.418212354472202</v>
       </c>
       <c r="J182" t="n">
         <v>-23</v>
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>1.470000028610229</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I184" t="n">
-        <v>4.081632573621466</v>
+        <v>4.026845611810072</v>
       </c>
       <c r="J184" t="n">
         <v>-30</v>
@@ -10857,7 +10857,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10942,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10952,14 +10952,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10969,14 +10969,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11044,7 +11044,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11088,14 +11088,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11105,14 +11105,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11122,14 +11122,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11139,14 +11139,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11214,7 +11214,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11248,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11258,14 +11258,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11282,7 +11282,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11299,7 +11299,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11316,7 +11316,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11326,14 +11326,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11350,7 +11350,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11428,14 +11428,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11452,7 +11452,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11462,14 +11462,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11479,14 +11479,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11513,14 +11513,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11530,14 +11530,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11547,14 +11547,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11564,14 +11564,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11581,14 +11581,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11605,7 +11605,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11615,14 +11615,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11639,7 +11639,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11649,14 +11649,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11673,7 +11673,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11690,7 +11690,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11700,14 +11700,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11717,14 +11717,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11734,14 +11734,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11758,7 +11758,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11775,7 +11775,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11785,14 +11785,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11809,7 +11809,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11826,7 +11826,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11836,14 +11836,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11853,14 +11853,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11877,7 +11877,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11979,7 +11979,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11989,14 +11989,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12006,14 +12006,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12023,14 +12023,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12040,14 +12040,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12057,14 +12057,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12074,14 +12074,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12091,14 +12091,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12108,14 +12108,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12125,14 +12125,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12149,7 +12149,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12159,14 +12159,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12200,7 +12200,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12217,7 +12217,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12227,14 +12227,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12244,14 +12244,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12261,14 +12261,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12278,14 +12278,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12302,7 +12302,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12312,14 +12312,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12336,7 +12336,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12346,14 +12346,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12363,14 +12363,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12380,14 +12380,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12397,14 +12397,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12421,7 +12421,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12431,14 +12431,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12472,7 +12472,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12482,14 +12482,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12523,7 +12523,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12591,7 +12591,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12625,7 +12625,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12642,7 +12642,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12659,7 +12659,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12676,7 +12676,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12727,7 +12727,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12744,7 +12744,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12761,7 +12761,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12771,14 +12771,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12812,7 +12812,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12829,7 +12829,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12839,14 +12839,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12880,7 +12880,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12897,7 +12897,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12907,14 +12907,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12924,14 +12924,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -12986,146 +12986,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EPH INVEST S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ILPRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>